--- a/events/Racice_2015_ECH/Racice_2015_ECH_Results.xlsx
+++ b/events/Racice_2015_ECH/Racice_2015_ECH_Results.xlsx
@@ -2522,6 +2522,11 @@
           <t>03:58.576</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2842,6 +2847,11 @@
           <t>03:31.828</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3747,6 +3757,11 @@
           <t>03:35.912</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4522,6 +4537,16 @@
           <t>42060</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5137,6 +5162,11 @@
           <t>42146</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6137,6 +6167,16 @@
           <t>03:35.204</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6267,6 +6307,11 @@
           <t>03:36.344</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>60759</t>
+        </is>
+      </c>
       <c r="S87" t="inlineStr">
         <is>
           <t>66277</t>
@@ -7442,6 +7487,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8457,6 +8507,11 @@
           <t>01:52.632</t>
         </is>
       </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10097,6 +10152,11 @@
           <t>01:50.892</t>
         </is>
       </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13802,6 +13862,11 @@
           <t>42060</t>
         </is>
       </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -15087,6 +15152,11 @@
           <t>36595</t>
         </is>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -16334,6 +16404,11 @@
           <t>03:52.680</t>
         </is>
       </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -18331,6 +18406,11 @@
           <t>03:33.960</t>
         </is>
       </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -19356,6 +19436,11 @@
           <t>03:38.744</t>
         </is>
       </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>60759</t>
+        </is>
+      </c>
       <c r="S282" t="inlineStr">
         <is>
           <t>66277</t>
@@ -19976,6 +20061,11 @@
           <t>41774</t>
         </is>
       </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -25071,6 +25161,11 @@
           <t>36595</t>
         </is>
       </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -26069,6 +26164,11 @@
           <t>03:41.292</t>
         </is>
       </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -27255,6 +27355,11 @@
           <t>03:59.388</t>
         </is>
       </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -27853,6 +27958,11 @@
           <t>03:36.612</t>
         </is>
       </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -28816,6 +28926,16 @@
           <t>42060</t>
         </is>
       </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -28965,6 +29085,11 @@
           <t>42146</t>
         </is>
       </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -29936,6 +30061,16 @@
           <t>03:38.552</t>
         </is>
       </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -31145,6 +31280,11 @@
           <t>36180</t>
         </is>
       </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
       <c r="T455" t="inlineStr">
         <is>
           <t>36183</t>
@@ -31381,9 +31521,19 @@
           <t>03:26.460</t>
         </is>
       </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>35912</t>
+        </is>
+      </c>
       <c r="S458" t="inlineStr">
         <is>
           <t>46671</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>35898</t>
         </is>
       </c>
     </row>
@@ -32120,6 +32270,11 @@
           <t>00:41.924</t>
         </is>
       </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -33845,6 +34000,11 @@
           <t>00:39.236</t>
         </is>
       </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -35780,6 +35940,11 @@
           <t>42060</t>
         </is>
       </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -36785,6 +36950,16 @@
           <t>00:37.676</t>
         </is>
       </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -37115,6 +37290,11 @@
           <t>00:41.784</t>
         </is>
       </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>60759</t>
+        </is>
+      </c>
       <c r="S546" t="inlineStr">
         <is>
           <t>66277</t>
@@ -37880,6 +38060,16 @@
           <t>00:34.092</t>
         </is>
       </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>51660</t>
+        </is>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -39200,6 +39390,11 @@
           <t>00:42.196</t>
         </is>
       </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -42909,6 +43104,11 @@
           <t>00:41.740</t>
         </is>
       </c>
+      <c r="R634" t="inlineStr">
+        <is>
+          <t>60759</t>
+        </is>
+      </c>
       <c r="S634" t="inlineStr">
         <is>
           <t>66277</t>
@@ -43459,6 +43659,16 @@
           <t>00:33.968</t>
         </is>
       </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>51660</t>
+        </is>
+      </c>
+      <c r="S642" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -45027,6 +45237,11 @@
           <t>01:56.656</t>
         </is>
       </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -45414,6 +45629,11 @@
           <t>01:50.580</t>
         </is>
       </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -47467,6 +47687,11 @@
           <t>42060</t>
         </is>
       </c>
+      <c r="S701" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -47869,6 +48094,16 @@
           <t>01:43.848</t>
         </is>
       </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S707" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -48363,6 +48598,11 @@
           <t>01:50.416</t>
         </is>
       </c>
+      <c r="R714" t="inlineStr">
+        <is>
+          <t>60759</t>
+        </is>
+      </c>
       <c r="S714" t="inlineStr">
         <is>
           <t>66277</t>
@@ -48430,6 +48670,11 @@
           <t>01:57.664</t>
         </is>
       </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
       <c r="S715" t="inlineStr">
         <is>
           <t>45223</t>
@@ -50986,6 +51231,11 @@
           <t>00:41.340</t>
         </is>
       </c>
+      <c r="R753" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -51909,6 +52159,11 @@
           <t>00:41.172</t>
         </is>
       </c>
+      <c r="R767" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -53033,6 +53288,11 @@
           <t>00:54.008</t>
         </is>
       </c>
+      <c r="R784" t="inlineStr">
+        <is>
+          <t>51670</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -53167,6 +53427,11 @@
           <t>42060</t>
         </is>
       </c>
+      <c r="S786" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -53775,6 +54040,16 @@
           <t>00:36.828</t>
         </is>
       </c>
+      <c r="R795" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="S795" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -55041,6 +55316,11 @@
           <t>22:19.250</t>
         </is>
       </c>
+      <c r="R813" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -57224,6 +57504,11 @@
           <t>20:21.560</t>
         </is>
       </c>
+      <c r="R846" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -57750,6 +58035,11 @@
           <t>21:10.770</t>
         </is>
       </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -58758,6 +59048,11 @@
       <c r="N870" t="n">
         <v>7</v>
       </c>
+      <c r="R870" t="inlineStr">
+        <is>
+          <t>47395</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -60005,6 +60300,11 @@
       <c r="N890" t="n">
         <v>3</v>
       </c>
+      <c r="R890" t="inlineStr">
+        <is>
+          <t>56556</t>
+        </is>
+      </c>
       <c r="X890" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -60449,6 +60749,11 @@
           <t>01:08.327</t>
         </is>
       </c>
+      <c r="R897" t="inlineStr">
+        <is>
+          <t>56560</t>
+        </is>
+      </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
@@ -60511,6 +60816,11 @@
           <t>01:23.231</t>
         </is>
       </c>
+      <c r="R898" t="inlineStr">
+        <is>
+          <t>60546</t>
+        </is>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -62292,6 +62602,11 @@
       <c r="N926" t="n">
         <v>6</v>
       </c>
+      <c r="R926" t="inlineStr">
+        <is>
+          <t>47395</t>
+        </is>
+      </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
@@ -62831,6 +63146,11 @@
           <t>01:00.124</t>
         </is>
       </c>
+      <c r="R935" t="inlineStr">
+        <is>
+          <t>61471</t>
+        </is>
+      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -63934,6 +64254,11 @@
       <c r="P952" t="inlineStr">
         <is>
           <t>01:03.676</t>
+        </is>
+      </c>
+      <c r="R952" t="inlineStr">
+        <is>
+          <t>56558</t>
         </is>
       </c>
     </row>
@@ -65203,7 +65528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D405"/>
+  <dimension ref="A1:D431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74116,6 +74441,578 @@
         </is>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>DRAHOKOUPIL</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>35912</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Tomas</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>JANDA</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>SHTYL</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Ilya</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>PERVUKHIN</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Alexey</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>KOROVASHKOV</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>PODOLSKAIA</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Viktor</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>MELANTEV</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Miika</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>NYKAENEN</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>42057</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Maryna</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>LITVINCHUK</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>KHUDZENKA</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Mikhail</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>PAVLOV</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>42148</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Svetlana</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>CHERNIGOVSKAYA</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>42411</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Helder</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Vitalii</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>TSURKAN</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>47395</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Igor</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>KOROBEYNIKOV</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>51660</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Dzmitry</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>TRATSIAKOU</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>51670</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>KLIMAVA</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>56556</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Leonid</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>KRYLOV</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>56558</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Larisa</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>VOLIK</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>56560</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Pavel</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>GROMOV</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>60546</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>SZPAK</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>60759</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Mykola</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>MATVIICHUK</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>61471</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Edina</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>MUELLER</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>68980</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Mikita</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>BORYKAU</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Gabor</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>SZABO</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Racice_2015_ECH/Racice_2015_ECH_Results.xlsx
+++ b/events/Racice_2015_ECH/Racice_2015_ECH_Results.xlsx
@@ -4687,6 +4687,11 @@
           <t>01:34.616</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S65" t="inlineStr">
         <is>
           <t>42337</t>
@@ -5157,6 +5162,11 @@
           <t>01:35.060</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="T71" t="inlineStr">
         <is>
           <t>42146</t>
@@ -7002,6 +7012,11 @@
           <t>03:22.036</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>42796</t>
+        </is>
+      </c>
       <c r="S97" t="inlineStr">
         <is>
           <t>42443</t>
@@ -9197,6 +9212,11 @@
           <t>02:00.464</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>35897</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13477,6 +13497,11 @@
           <t>02:58.428</t>
         </is>
       </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>45352</t>
+        </is>
+      </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>44425</t>
@@ -13992,6 +14017,11 @@
           <t>01:44.844</t>
         </is>
       </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="S201" t="inlineStr">
         <is>
           <t>42146</t>
@@ -14057,6 +14087,11 @@
           <t>01:45.604</t>
         </is>
       </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>35562</t>
+        </is>
+      </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>35560</t>
@@ -14122,6 +14157,11 @@
           <t>01:45.908</t>
         </is>
       </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S203" t="inlineStr">
         <is>
           <t>42337</t>
@@ -20126,6 +20166,11 @@
           <t>03:18.868</t>
         </is>
       </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>42796</t>
+        </is>
+      </c>
       <c r="S292" t="inlineStr">
         <is>
           <t>42443</t>
@@ -21056,6 +21101,11 @@
           <t>01:56.176</t>
         </is>
       </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>35897</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -23576,6 +23626,11 @@
           <t>02:55.677</t>
         </is>
       </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>45352</t>
+        </is>
+      </c>
       <c r="S345" t="inlineStr">
         <is>
           <t>44425</t>
@@ -24186,6 +24241,11 @@
           <t>01:43.712</t>
         </is>
       </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S353" t="inlineStr">
         <is>
           <t>42337</t>
@@ -24321,6 +24381,11 @@
           <t>01:44.844</t>
         </is>
       </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>35562</t>
+        </is>
+      </c>
       <c r="S355" t="inlineStr">
         <is>
           <t>35560</t>
@@ -29080,6 +29145,11 @@
           <t>01:37.804</t>
         </is>
       </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="T425" t="inlineStr">
         <is>
           <t>42146</t>
@@ -29316,6 +29386,11 @@
           <t>01:39.556</t>
         </is>
       </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S428" t="inlineStr">
         <is>
           <t>42337</t>
@@ -31536,6 +31611,11 @@
           <t>35898</t>
         </is>
       </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>35556</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -36070,6 +36150,11 @@
           <t>00:38.888</t>
         </is>
       </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="S528" t="inlineStr">
         <is>
           <t>42146</t>
@@ -36205,6 +36290,11 @@
           <t>00:39.256</t>
         </is>
       </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S530" t="inlineStr">
         <is>
           <t>42337</t>
@@ -36610,6 +36700,11 @@
           <t>00:39.348</t>
         </is>
       </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>35562</t>
+        </is>
+      </c>
       <c r="S536" t="inlineStr">
         <is>
           <t>35560</t>
@@ -42349,6 +42444,11 @@
           <t>00:38.740</t>
         </is>
       </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S623" t="inlineStr">
         <is>
           <t>42337</t>
@@ -44309,6 +44409,11 @@
           <t>02:01.468</t>
         </is>
       </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>35897</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -47404,6 +47509,11 @@
           <t>03:02.364</t>
         </is>
       </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>45352</t>
+        </is>
+      </c>
       <c r="S697" t="inlineStr">
         <is>
           <t>44425</t>
@@ -47826,6 +47936,11 @@
           <t>01:48.428</t>
         </is>
       </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="S703" t="inlineStr">
         <is>
           <t>42146</t>
@@ -47893,6 +48008,11 @@
           <t>01:48.580</t>
         </is>
       </c>
+      <c r="R704" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S704" t="inlineStr">
         <is>
           <t>42337</t>
@@ -48027,6 +48147,11 @@
           <t>01:49.604</t>
         </is>
       </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>35562</t>
+        </is>
+      </c>
       <c r="S706" t="inlineStr">
         <is>
           <t>35560</t>
@@ -53767,6 +53892,11 @@
           <t>00:39.828</t>
         </is>
       </c>
+      <c r="R791" t="inlineStr">
+        <is>
+          <t>35562</t>
+        </is>
+      </c>
       <c r="S791" t="inlineStr">
         <is>
           <t>35560</t>
@@ -53834,6 +53964,11 @@
           <t>00:39.840</t>
         </is>
       </c>
+      <c r="R792" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
       <c r="S792" t="inlineStr">
         <is>
           <t>42337</t>
@@ -53973,6 +54108,11 @@
           <t>00:40.072</t>
         </is>
       </c>
+      <c r="R794" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
       <c r="S794" t="inlineStr">
         <is>
           <t>42146</t>
@@ -58877,6 +59017,11 @@
           <t>00:52.936</t>
         </is>
       </c>
+      <c r="R867" t="inlineStr">
+        <is>
+          <t>54626</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -62485,6 +62630,11 @@
           <t>00:50.256</t>
         </is>
       </c>
+      <c r="R924" t="inlineStr">
+        <is>
+          <t>54626</t>
+        </is>
+      </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -63610,6 +63760,11 @@
           <t>01:09.292</t>
         </is>
       </c>
+      <c r="R942" t="inlineStr">
+        <is>
+          <t>61309</t>
+        </is>
+      </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
@@ -64061,6 +64216,11 @@
       <c r="P949" t="inlineStr">
         <is>
           <t>00:57.184</t>
+        </is>
+      </c>
+      <c r="R949" t="inlineStr">
+        <is>
+          <t>46444</t>
         </is>
       </c>
     </row>
@@ -65528,7 +65688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D431"/>
+  <dimension ref="A1:D441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75013,6 +75173,226 @@
         </is>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>JØRGENSEN</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Elena</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>ANYSHINA</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>42796</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>FITZSIMONS</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>35897</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Lucie</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>MATOUNKOVÁ</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>45352</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Denis</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>MISAK</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>35562</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>LEHACI</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>35556</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Radek</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>MINKOVSKÝ</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>54626</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Or</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>ATATO</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>61309</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Elmar</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>STERNACH</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>46444</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Nataliia</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>LAGUTENKO</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
